--- a/doc/Doc_KSA/2418_DemonstrateurGraphique_Journal_KSA.xlsx
+++ b/doc/Doc_KSA/2418_DemonstrateurGraphique_Journal_KSA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\microchip\harmony\v2_06\apps\PROJ\PRJ_2418_demosntrateurGraphique-\doc\Doc_KSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35C7EAB-F156-407A-AEE3-DD91346B84C7}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7E6C2D-F5F0-4A18-A73B-D7B3DDCBBA13}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Prise en main projet =&gt; PMP</t>
   </si>
@@ -40,6 +40,12 @@
   </si>
   <si>
     <t>(PMP) Correction CDC + Configuration MPLABX</t>
+  </si>
+  <si>
+    <t>(PMP) Code basique sur MPLABX</t>
+  </si>
+  <si>
+    <t>Ajout README + Création fichier propre pour librairie FT812</t>
   </si>
 </sst>
 </file>
@@ -374,12 +380,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D3:E6"/>
+  <dimension ref="D3:E8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
     <col min="4" max="4" width="11.42578125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="45.7109375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="73.140625" style="2" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
@@ -415,6 +421,22 @@
         <v>4</v>
       </c>
     </row>
+    <row r="7" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D7" s="1">
+        <v>46085</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D8" s="1">
+        <v>46092</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/doc/Doc_KSA/2418_DemonstrateurGraphique_Journal_KSA.xlsx
+++ b/doc/Doc_KSA/2418_DemonstrateurGraphique_Journal_KSA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\microchip\harmony\v2_06\apps\PROJ\PRJ_2418_demosntrateurGraphique-\doc\Doc_KSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7E6C2D-F5F0-4A18-A73B-D7B3DDCBBA13}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF04C47-ECAF-416C-8BE2-0F67F1708621}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Prise en main projet =&gt; PMP</t>
   </si>
@@ -46,6 +46,15 @@
   </si>
   <si>
     <t>Ajout README + Création fichier propre pour librairie FT812</t>
+  </si>
+  <si>
+    <t>Ajout fonction d'écriture pour FT812 + fonction d'init pour FT812</t>
+  </si>
+  <si>
+    <t>Création fichiers pour drover LCD + Mise au propre librairie FT812</t>
+  </si>
+  <si>
+    <t>Test de la fonction de lécture du FT812 | Lécture de REG_ID</t>
   </si>
 </sst>
 </file>
@@ -380,7 +389,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D3:E8"/>
+  <dimension ref="D3:E12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -437,6 +446,35 @@
         <v>6</v>
       </c>
     </row>
+    <row r="9" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D9" s="1">
+        <v>46099</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D10" s="1">
+        <v>46106</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D11" s="1">
+        <v>46113</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D12" s="1">
+        <v>46134</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/doc/Doc_KSA/2418_DemonstrateurGraphique_Journal_KSA.xlsx
+++ b/doc/Doc_KSA/2418_DemonstrateurGraphique_Journal_KSA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\microchip\harmony\v2_06\apps\PROJ\PRJ_2418_demosntrateurGraphique-\doc\Doc_KSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF04C47-ECAF-416C-8BE2-0F67F1708621}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{879B47DA-C82E-4CA9-B393-EAC64BAE3911}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Prise en main projet =&gt; PMP</t>
   </si>
@@ -55,6 +55,12 @@
   </si>
   <si>
     <t>Test de la fonction de lécture du FT812 | Lécture de REG_ID</t>
+  </si>
+  <si>
+    <t>Modification README + Mesures</t>
+  </si>
+  <si>
+    <t>Modification de la lib. pour le F812</t>
   </si>
 </sst>
 </file>
@@ -389,7 +395,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D3:E12"/>
+  <dimension ref="D3:E13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -474,6 +480,17 @@
       <c r="D12" s="1">
         <v>46134</v>
       </c>
+      <c r="E12" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D13" s="1">
+        <v>46141</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/doc/Doc_KSA/2418_DemonstrateurGraphique_Journal_KSA.xlsx
+++ b/doc/Doc_KSA/2418_DemonstrateurGraphique_Journal_KSA.xlsx
@@ -8,24 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\microchip\harmony\v2_06\apps\PROJ\PRJ_2418_demosntrateurGraphique-\doc\Doc_KSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{879B47DA-C82E-4CA9-B393-EAC64BAE3911}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EDC5C17-5E94-4324-B080-8B04DC727038}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4890" yWindow="2865" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Prise en main projet =&gt; PMP</t>
   </si>
@@ -61,6 +69,9 @@
   </si>
   <si>
     <t>Modification de la lib. pour le F812</t>
+  </si>
+  <si>
+    <t>Validation lécture REG_ID / Test autre lécture NOK</t>
   </si>
 </sst>
 </file>
@@ -395,7 +406,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D3:E13"/>
+  <dimension ref="D3:E14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -492,6 +503,14 @@
         <v>11</v>
       </c>
     </row>
+    <row r="14" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D14" s="1">
+        <v>46148</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/doc/Doc_KSA/2418_DemonstrateurGraphique_Journal_KSA.xlsx
+++ b/doc/Doc_KSA/2418_DemonstrateurGraphique_Journal_KSA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\microchip\harmony\v2_06\apps\PROJ\PRJ_2418_demosntrateurGraphique-\doc\Doc_KSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EDC5C17-5E94-4324-B080-8B04DC727038}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FD123D-8CB1-483C-855B-3173C48B5752}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4890" yWindow="2865" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Prise en main projet =&gt; PMP</t>
   </si>
@@ -72,6 +72,12 @@
   </si>
   <si>
     <t>Validation lécture REG_ID / Test autre lécture NOK</t>
+  </si>
+  <si>
+    <t>Validation lécture de la ROM | Lécture RAM NOK probléme init FT812</t>
+  </si>
+  <si>
+    <t>Modif. README ajout schéma | Test corr. Init pour lire RAM</t>
   </si>
 </sst>
 </file>
@@ -406,7 +412,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D3:E14"/>
+  <dimension ref="D3:E16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -511,6 +517,22 @@
         <v>12</v>
       </c>
     </row>
+    <row r="15" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D15" s="1">
+        <v>46155</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D16" s="1">
+        <v>46162</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/doc/Doc_KSA/2418_DemonstrateurGraphique_Journal_KSA.xlsx
+++ b/doc/Doc_KSA/2418_DemonstrateurGraphique_Journal_KSA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\microchip\harmony\v2_06\apps\PROJ\PRJ_2418_demosntrateurGraphique-\doc\Doc_KSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FD123D-8CB1-483C-855B-3173C48B5752}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D9D1217-C9C8-4B55-806D-373B7142C8A6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Prise en main projet =&gt; PMP</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>Modif. README ajout schéma | Test corr. Init pour lire RAM</t>
+  </si>
+  <si>
+    <t>Modif. README | Prise mesures test fonctions | Maj. Fonction write 16 et 32 bits</t>
   </si>
 </sst>
 </file>
@@ -412,7 +415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="D3:E16"/>
+  <dimension ref="D3:E17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="9.140625" style="2"/>
@@ -533,7 +536,16 @@
         <v>14</v>
       </c>
     </row>
+    <row r="17" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D17" s="1">
+        <v>46169</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>